--- a/public/exports/12881517.xlsx
+++ b/public/exports/12881517.xlsx
@@ -81,16 +81,16 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10126525</t>
+          <t xml:space="preserve">2032620</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F2">
-        <v>884</v>
+        <v>651</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -136,11 +136,11 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
       <c r="F3">
-        <v>651</v>
+        <v>540</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -186,11 +186,11 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F4">
-        <v>540</v>
+        <v>1250</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -236,11 +236,11 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F5">
-        <v>1250</v>
+        <v>1825</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -281,16 +281,16 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032620</t>
+          <t xml:space="preserve">230811, 230812</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F6">
-        <v>1825</v>
+        <v>3045</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -631,25 +631,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2092475</t>
+          <t xml:space="preserve">10126525</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F13">
-        <v>741</v>
+        <v>884</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">311209844</t>
+          <t xml:space="preserve">200013195</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-04</t>
+          <t xml:space="preserve">2019-05-01</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2091521</t>
+          <t xml:space="preserve">2092475</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -690,26 +690,26 @@
         </is>
       </c>
       <c r="F14">
-        <v>611</v>
+        <v>741</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">311200341</t>
+          <t xml:space="preserve">311209844</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-13</t>
+          <t xml:space="preserve">2026-07-04</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2092291</t>
+          <t xml:space="preserve">2091521</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -740,11 +740,11 @@
         </is>
       </c>
       <c r="F15">
-        <v>313</v>
+        <v>611</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">311200340</t>
+          <t xml:space="preserve">311200341</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -781,25 +781,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">10126525</t>
+          <t xml:space="preserve">2092291</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F16">
-        <v>495</v>
+        <v>313</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">311223549</t>
+          <t xml:space="preserve">311200340</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-19</t>
+          <t xml:space="preserve">2026-09-13</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -831,20 +831,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030964</t>
+          <t xml:space="preserve">10126525</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F17">
-        <v>400</v>
+        <v>495</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">311223547</t>
+          <t xml:space="preserve">311223549</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -886,11 +886,11 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F18">
-        <v>337</v>
+        <v>400</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -931,25 +931,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">10126525</t>
+          <t xml:space="preserve">2030964</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F19">
-        <v>418</v>
+        <v>337</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">311224560</t>
+          <t xml:space="preserve">311223547</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-25</t>
+          <t xml:space="preserve">2027-01-19</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -981,25 +981,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">10087996</t>
+          <t xml:space="preserve">10126525</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F20">
-        <v>1110</v>
+        <v>418</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">311225391</t>
+          <t xml:space="preserve">311224560</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-30</t>
+          <t xml:space="preserve">2027-01-25</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1031,20 +1031,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032620</t>
+          <t xml:space="preserve">10087996</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">30</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F21">
-        <v>354</v>
+        <v>1110</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">311225385</t>
+          <t xml:space="preserve">311225391</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1086,15 +1086,15 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">30</t>
         </is>
       </c>
       <c r="F22">
-        <v>449</v>
+        <v>354</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">311225395</t>
+          <t xml:space="preserve">311225385</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1131,20 +1131,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034086</t>
+          <t xml:space="preserve">2032620</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="F23">
-        <v>348</v>
+        <v>449</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">311225387</t>
+          <t xml:space="preserve">311225395</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1186,11 +1186,11 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F24">
-        <v>376</v>
+        <v>348</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1231,20 +1231,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">8752205</t>
+          <t xml:space="preserve">2034086</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F25">
-        <v>658</v>
+        <v>376</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">311225392</t>
+          <t xml:space="preserve">311225387</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2092630</t>
+          <t xml:space="preserve">8752205</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1290,16 +1290,16 @@
         </is>
       </c>
       <c r="F26">
-        <v>431</v>
+        <v>658</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">311226040</t>
+          <t xml:space="preserve">311225392</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-01</t>
+          <t xml:space="preserve">2027-01-30</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">8752208</t>
+          <t xml:space="preserve">2092630</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1340,16 +1340,16 @@
         </is>
       </c>
       <c r="F27">
-        <v>1246</v>
+        <v>431</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">311227426</t>
+          <t xml:space="preserve">311226040</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-09</t>
+          <t xml:space="preserve">2027-02-01</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2092314</t>
+          <t xml:space="preserve">8752208</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1390,16 +1390,16 @@
         </is>
       </c>
       <c r="F28">
-        <v>258</v>
+        <v>1246</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">311228158</t>
+          <t xml:space="preserve">311227426</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-13</t>
+          <t xml:space="preserve">2027-02-09</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1431,20 +1431,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2092475</t>
+          <t xml:space="preserve">2092314</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F29">
-        <v>372</v>
+        <v>258</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">311228161</t>
+          <t xml:space="preserve">311228158</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1481,25 +1481,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">8752265</t>
+          <t xml:space="preserve">2092475</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F30">
-        <v>263</v>
+        <v>372</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">311234279</t>
+          <t xml:space="preserve">311228161</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-15</t>
+          <t xml:space="preserve">2027-02-13</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1581,25 +1581,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032700</t>
+          <t xml:space="preserve">2091437</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F32">
-        <v>346</v>
+        <v>382</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">311246253</t>
+          <t xml:space="preserve">311247075</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-09</t>
+          <t xml:space="preserve">2027-05-11</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1636,20 +1636,20 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F33">
-        <v>382</v>
+        <v>492</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">311247075</t>
+          <t xml:space="preserve">311251338</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-11</t>
+          <t xml:space="preserve">2027-06-01</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1686,11 +1686,11 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F34">
-        <v>492</v>
+        <v>637</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1736,11 +1736,11 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F35">
-        <v>637</v>
+        <v>2044</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1786,11 +1786,11 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F36">
-        <v>2044</v>
+        <v>1136</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1831,25 +1831,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2091437</t>
+          <t xml:space="preserve">8752265</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F37">
-        <v>1136</v>
+        <v>263</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">311251338</t>
+          <t xml:space="preserve">311253147</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-01</t>
+          <t xml:space="preserve">2027-06-12</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">311293749</t>
+          <t xml:space="preserve">311293736</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2294,7 +2294,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">311293749</t>
+          <t xml:space="preserve">311293736</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2331,20 +2331,20 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">230811, 230812</t>
+          <t xml:space="preserve">2032700</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F47">
-        <v>3045</v>
+        <v>346</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">311293732</t>
+          <t xml:space="preserve">311293736</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">

--- a/public/exports/12881517.xlsx
+++ b/public/exports/12881517.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J54"/>
+  <dimension ref="A1:L54"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -29,35 +29,45 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Adresse</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Postnr.</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t xml:space="preserve">BFE-nummer</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t xml:space="preserve">Bygningsnummer</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t xml:space="preserve">Areal (m²)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t xml:space="preserve">EM-nummer</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -81,33 +91,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kirkevej 8</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2791</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032620</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t xml:space="preserve">10</t>
         </is>
       </c>
-      <c r="F2">
+      <c r="H2">
         <v>651</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -131,33 +151,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t xml:space="preserve">Halvejen 9</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2791</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032620</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t xml:space="preserve">37</t>
         </is>
       </c>
-      <c r="F3">
+      <c r="H3">
         <v>540</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -181,33 +211,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kirkevej 8</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2791</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032620</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="F4">
+      <c r="H4">
         <v>1250</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -231,33 +271,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kirkevej 8</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2791</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032620</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="F5">
+      <c r="H5">
         <v>1825</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -281,33 +331,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t xml:space="preserve">Engvej 20A</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2791</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t xml:space="preserve">230811, 230812</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F6">
+      <c r="H6">
         <v>3045</v>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -331,33 +391,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Strandjægervej 3</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2791</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t xml:space="preserve">230813</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F7">
+      <c r="H7">
         <v>1309</v>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -381,33 +451,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t xml:space="preserve">Strandjægervej 3</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2791</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t xml:space="preserve">230813</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F8">
+      <c r="H8">
         <v>2063</v>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -431,33 +511,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t xml:space="preserve">Strandjægervej 3</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2791</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t xml:space="preserve">230813, 230814</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F9">
+      <c r="H9">
         <v>2927</v>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -481,33 +571,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Halvejen 5</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2791</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t xml:space="preserve">711463, 2032620</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t xml:space="preserve">38</t>
         </is>
       </c>
-      <c r="F10">
+      <c r="H10">
         <v>450</v>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -531,33 +631,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t xml:space="preserve">Engvej 20B</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2791</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t xml:space="preserve">8043122</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F11">
+      <c r="H11">
         <v>472</v>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -581,33 +691,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t xml:space="preserve">Strandjægervej 17</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2791</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t xml:space="preserve">9070842</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F12">
+      <c r="H12">
         <v>610</v>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -631,33 +751,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hartkornsvej 30</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2791</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t xml:space="preserve">10126525</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t xml:space="preserve">17</t>
         </is>
       </c>
-      <c r="F13">
+      <c r="H13">
         <v>884</v>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t xml:space="preserve">200013195</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-05-01</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -681,33 +811,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t xml:space="preserve">Engvej 26</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2791</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t xml:space="preserve">2092475</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F14">
+      <c r="H14">
         <v>741</v>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t xml:space="preserve">311209844</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-07-04</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -731,33 +871,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t xml:space="preserve">Engvej 2</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2791</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t xml:space="preserve">2091521</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F15">
+      <c r="H15">
         <v>611</v>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t xml:space="preserve">311200341</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-09-13</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -781,33 +931,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t xml:space="preserve">Engvej 1</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2791</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t xml:space="preserve">2092291</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F16">
+      <c r="H16">
         <v>313</v>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t xml:space="preserve">311200340</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-09-13</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -831,33 +991,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hartkornsvej 32</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2791</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t xml:space="preserve">10126525</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t xml:space="preserve">10</t>
         </is>
       </c>
-      <c r="F17">
+      <c r="H17">
         <v>495</v>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t xml:space="preserve">311223549</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-01-19</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -881,33 +1051,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t xml:space="preserve">Høgevænget 7</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2791</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030964</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F18">
+      <c r="H18">
         <v>400</v>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t xml:space="preserve">311223547</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-01-19</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -931,33 +1111,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t xml:space="preserve">Høgevænget 5</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2791</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030964</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F19">
+      <c r="H19">
         <v>337</v>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t xml:space="preserve">311223547</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-01-19</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -981,33 +1171,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hartkornsvej 34</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2791</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t xml:space="preserve">10126525</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t xml:space="preserve">11</t>
         </is>
       </c>
-      <c r="F20">
+      <c r="H20">
         <v>418</v>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t xml:space="preserve">311224560</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-01-25</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1031,33 +1231,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t xml:space="preserve">Køjevænget 91</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2791</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t xml:space="preserve">10087996</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F21">
+      <c r="H21">
         <v>1110</v>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t xml:space="preserve">311225391</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-01-30</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1081,33 +1291,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t xml:space="preserve">Halvejen 1</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2791</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032620</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t xml:space="preserve">30</t>
         </is>
       </c>
-      <c r="F22">
+      <c r="H22">
         <v>354</v>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t xml:space="preserve">311225385</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-01-30</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1131,33 +1351,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t xml:space="preserve">Halvejen 7</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2791</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032620</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t xml:space="preserve">35</t>
         </is>
       </c>
-      <c r="F23">
+      <c r="H23">
         <v>449</v>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t xml:space="preserve">311225395</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-01-30</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
+      <c r="K23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1181,33 +1411,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t xml:space="preserve">Søvej 1A</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2791</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034086</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F24">
+      <c r="H24">
         <v>348</v>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t xml:space="preserve">311225387</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-01-30</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
+      <c r="K24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1231,33 +1471,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t xml:space="preserve">Søvej 1A</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2791</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034086</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F25">
+      <c r="H25">
         <v>376</v>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t xml:space="preserve">311225387</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-01-30</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
+      <c r="K25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1281,33 +1531,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t xml:space="preserve">Harevænget 1</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2791</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t xml:space="preserve">8752205</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F26">
+      <c r="H26">
         <v>658</v>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t xml:space="preserve">311225392</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-01-30</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
+      <c r="K26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1331,33 +1591,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t xml:space="preserve">Søndre Tangvej 26</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2791</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t xml:space="preserve">2092630</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F27">
+      <c r="H27">
         <v>431</v>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t xml:space="preserve">311226040</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-02-01</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
+      <c r="K27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1381,33 +1651,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kalvebodvej 255</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2791</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t xml:space="preserve">8752208</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F28">
+      <c r="H28">
         <v>1246</v>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t xml:space="preserve">311227426</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-02-09</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
+      <c r="K28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1431,33 +1711,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
+          <t xml:space="preserve">Stationsvej 5</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2791</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
           <t xml:space="preserve">2092314</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F29">
+      <c r="H29">
         <v>258</v>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t xml:space="preserve">311228158</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-02-13</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
+      <c r="K29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1481,33 +1771,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t xml:space="preserve">Engvej 22</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2791</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
           <t xml:space="preserve">2092475</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F30">
+      <c r="H30">
         <v>372</v>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t xml:space="preserve">311228161</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-02-13</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
+      <c r="K30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1531,33 +1831,43 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rødtjørnen 60C</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2791</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
           <t xml:space="preserve">2092694</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F31">
+      <c r="H31">
         <v>262</v>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t xml:space="preserve">311245791</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-05-06</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
+      <c r="K31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1581,33 +1891,43 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vestgrønningen 7</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2791</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
           <t xml:space="preserve">2091437</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F32">
+      <c r="H32">
         <v>382</v>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t xml:space="preserve">311247075</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-05-11</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
+      <c r="K32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1631,33 +1951,43 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vestgrønningen 11</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2791</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
           <t xml:space="preserve">2091437</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F33">
+      <c r="H33">
         <v>492</v>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t xml:space="preserve">311251338</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-06-01</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
+      <c r="K33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1681,33 +2011,43 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vestgrønningen 9</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2791</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
           <t xml:space="preserve">2091437</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F34">
+      <c r="H34">
         <v>637</v>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t xml:space="preserve">311251338</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-06-01</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
+      <c r="K34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1731,33 +2071,43 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vestgrønningen 5</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2791</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
           <t xml:space="preserve">2091437</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F35">
+      <c r="H35">
         <v>2044</v>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t xml:space="preserve">311251338</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-06-01</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
+      <c r="K35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1781,33 +2131,43 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vestgrønningen 7</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2791</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
           <t xml:space="preserve">2091437</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F36">
+      <c r="H36">
         <v>1136</v>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t xml:space="preserve">311251338</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-06-01</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
+      <c r="K36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1831,33 +2191,43 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gl. Havn 2</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2791</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
           <t xml:space="preserve">8752265</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t xml:space="preserve">10</t>
         </is>
       </c>
-      <c r="F37">
+      <c r="H37">
         <v>263</v>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311253147</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
+      <c r="I37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311253233</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-06-12</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
+      <c r="K37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1881,33 +2251,43 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
+          <t xml:space="preserve">Strandlinien 3</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2791</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
           <t xml:space="preserve">8752265</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F38">
+      <c r="H38">
         <v>258</v>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311253129</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
+      <c r="I38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311253233</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-06-12</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
+      <c r="K38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1931,33 +2311,43 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kirkevej 8</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2791</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032620</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t xml:space="preserve">12</t>
         </is>
       </c>
-      <c r="F39">
+      <c r="H39">
         <v>560</v>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t xml:space="preserve">311257954</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-06-30</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
+      <c r="K39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1981,33 +2371,43 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kirkevej 8</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2791</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032620</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F40">
+      <c r="H40">
         <v>549</v>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t xml:space="preserve">311257941</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-06-30</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
+      <c r="K40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2031,33 +2431,43 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kirkevej 8</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2791</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032620</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F41">
+      <c r="H41">
         <v>339</v>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t xml:space="preserve">311257941</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-06-30</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
+      <c r="K41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2081,33 +2491,43 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kirkevej 8</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2791</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032620</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F42">
+      <c r="H42">
         <v>1279</v>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t xml:space="preserve">311257941</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-06-30</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
+      <c r="K42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2131,33 +2551,43 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kirkevej 8</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2791</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032620</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F43">
+      <c r="H43">
         <v>280</v>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t xml:space="preserve">311257941</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-06-30</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
+      <c r="K43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2181,33 +2611,43 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ndr Dragørvej 160</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2791</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033840</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F44">
+      <c r="H44">
         <v>1074</v>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t xml:space="preserve">311257703</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-06-30</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
+      <c r="K44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2231,33 +2671,43 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kirkevej 7</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2791</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032700</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F45">
+      <c r="H45">
         <v>3210</v>
       </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311293736</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
+      <c r="I45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311293749</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-01-22</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
+      <c r="K45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2281,33 +2731,43 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kirkevej 7</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2791</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032700</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F46">
+      <c r="H46">
         <v>486</v>
       </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311293736</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
+      <c r="I46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311293749</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-01-22</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
+      <c r="K46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2331,33 +2791,43 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kirkevej 11</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2791</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032700</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="F47">
+      <c r="H47">
         <v>346</v>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t xml:space="preserve">311293736</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-01-22</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
+      <c r="K47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2381,33 +2851,43 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hartkornsvej 30</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2791</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
           <t xml:space="preserve">10126525</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F48">
+      <c r="H48">
         <v>7872</v>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t xml:space="preserve">311364408</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-03-13</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
+      <c r="K48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2431,33 +2911,43 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hartkornsvej 30</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2791</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
           <t xml:space="preserve">10126525</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F49">
+      <c r="H49">
         <v>725</v>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t xml:space="preserve">311364408</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-03-13</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
+      <c r="K49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2481,33 +2971,43 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hartkornsvej 30</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2791</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
           <t xml:space="preserve">10126525</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F50">
+      <c r="H50">
         <v>725</v>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t xml:space="preserve">311364408</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-03-13</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
+      <c r="K50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2531,33 +3031,43 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
+          <t xml:space="preserve">Halvejen 3</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2791</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032620</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t xml:space="preserve">14</t>
         </is>
       </c>
-      <c r="F51">
+      <c r="H51">
         <v>3950</v>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t xml:space="preserve">311394561</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-08-23</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
+      <c r="K51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2581,33 +3091,43 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
+          <t xml:space="preserve">Halvejen 3</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2791</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032620</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t xml:space="preserve">15</t>
         </is>
       </c>
-      <c r="F52">
+      <c r="H52">
         <v>2145</v>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t xml:space="preserve">311394562</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-08-23</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
+      <c r="K52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2631,33 +3151,43 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kirkevej 24</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2791</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032645</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F53">
+      <c r="H53">
         <v>748</v>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t xml:space="preserve">311805659</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-01-13</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
+      <c r="K53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2681,39 +3211,49 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kongevejen 11A</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2791</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
           <t xml:space="preserve">2091749</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F54">
+      <c r="H54">
         <v>515</v>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t xml:space="preserve">311805660</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-01-13</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
+      <c r="K54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J54"/>
+  <autoFilter ref="A1:L54"/>
 </worksheet>
 </file>
--- a/public/exports/12881517.xlsx
+++ b/public/exports/12881517.xlsx
@@ -91,7 +91,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkevej 8</t>
+          <t xml:space="preserve">Engvej 20B</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -101,16 +101,16 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032620</t>
+          <t xml:space="preserve">8043122</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H2">
-        <v>651</v>
+        <v>472</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -151,7 +151,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Halvejen 9</t>
+          <t xml:space="preserve">Halvejen 5</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -161,16 +161,16 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032620</t>
+          <t xml:space="preserve">711463, 2032620</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t xml:space="preserve">38</t>
         </is>
       </c>
       <c r="H3">
-        <v>540</v>
+        <v>450</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -211,7 +211,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkevej 8</t>
+          <t xml:space="preserve">Halvejen 9</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -226,11 +226,11 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
       <c r="H4">
-        <v>1250</v>
+        <v>540</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -286,11 +286,11 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H5">
-        <v>1825</v>
+        <v>651</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -331,7 +331,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engvej 20A</t>
+          <t xml:space="preserve">Kirkevej 8</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -341,16 +341,16 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">230811, 230812</t>
+          <t xml:space="preserve">2032620</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H6">
-        <v>3045</v>
+        <v>1250</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -391,7 +391,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandjægervej 3</t>
+          <t xml:space="preserve">Kirkevej 8</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -401,16 +401,16 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">230813</t>
+          <t xml:space="preserve">2032620</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H7">
-        <v>1309</v>
+        <v>1825</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -451,7 +451,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandjægervej 3</t>
+          <t xml:space="preserve">Strandjægervej 17</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -461,16 +461,16 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">230813</t>
+          <t xml:space="preserve">9070842</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H8">
-        <v>2063</v>
+        <v>610</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -521,16 +521,16 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">230813, 230814</t>
+          <t xml:space="preserve">230813</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H9">
-        <v>2927</v>
+        <v>1309</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -571,7 +571,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Halvejen 5</t>
+          <t xml:space="preserve">Strandjægervej 3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -581,16 +581,16 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">711463, 2032620</t>
+          <t xml:space="preserve">230813</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">38</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H10">
-        <v>450</v>
+        <v>2063</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -631,7 +631,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engvej 20B</t>
+          <t xml:space="preserve">Strandjægervej 3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -641,16 +641,16 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">8043122</t>
+          <t xml:space="preserve">230813, 230814</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H11">
-        <v>472</v>
+        <v>2927</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandjægervej 17</t>
+          <t xml:space="preserve">Hartkornsvej 30</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -701,30 +701,30 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">9070842</t>
+          <t xml:space="preserve">10126525</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="H12">
-        <v>610</v>
+        <v>884</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200013195</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-05-01</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hartkornsvej 30</t>
+          <t xml:space="preserve">Engvej 26</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -761,25 +761,25 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">10126525</t>
+          <t xml:space="preserve">2092475</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H13">
-        <v>884</v>
+        <v>741</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t xml:space="preserve">200013195</t>
+          <t xml:space="preserve">311209844</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-05-01</t>
+          <t xml:space="preserve">2026-07-04</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engvej 26</t>
+          <t xml:space="preserve">Engvej 1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2092475</t>
+          <t xml:space="preserve">2092291</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -830,26 +830,26 @@
         </is>
       </c>
       <c r="H14">
-        <v>741</v>
+        <v>313</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve">311209844</t>
+          <t xml:space="preserve">311200340</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-04</t>
+          <t xml:space="preserve">2026-09-13</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -931,7 +931,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engvej 1</t>
+          <t xml:space="preserve">Hartkornsvej 32</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -941,25 +941,25 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2092291</t>
+          <t xml:space="preserve">10126525</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H16">
-        <v>313</v>
+        <v>495</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve">311200340</t>
+          <t xml:space="preserve">311223549</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-13</t>
+          <t xml:space="preserve">2027-01-19</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hartkornsvej 32</t>
+          <t xml:space="preserve">Høgevænget 5</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1001,20 +1001,20 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">10126525</t>
+          <t xml:space="preserve">2030964</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H17">
-        <v>495</v>
+        <v>337</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">311223549</t>
+          <t xml:space="preserve">311223547</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høgevænget 5</t>
+          <t xml:space="preserve">Hartkornsvej 34</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1121,25 +1121,25 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030964</t>
+          <t xml:space="preserve">10126525</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H19">
-        <v>337</v>
+        <v>418</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">311223547</t>
+          <t xml:space="preserve">311224560</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-19</t>
+          <t xml:space="preserve">2027-01-25</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hartkornsvej 34</t>
+          <t xml:space="preserve">Halvejen 1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1181,25 +1181,25 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">10126525</t>
+          <t xml:space="preserve">2032620</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">30</t>
         </is>
       </c>
       <c r="H20">
-        <v>418</v>
+        <v>354</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">311224560</t>
+          <t xml:space="preserve">311225385</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-25</t>
+          <t xml:space="preserve">2027-01-30</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Køjevænget 91</t>
+          <t xml:space="preserve">Halvejen 7</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1241,20 +1241,20 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">10087996</t>
+          <t xml:space="preserve">2032620</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="H21">
-        <v>1110</v>
+        <v>449</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">311225391</t>
+          <t xml:space="preserve">311225395</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Halvejen 1</t>
+          <t xml:space="preserve">Harevænget 1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1301,20 +1301,20 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032620</t>
+          <t xml:space="preserve">8752205</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">30</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H22">
-        <v>354</v>
+        <v>658</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">311225385</t>
+          <t xml:space="preserve">311225392</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Halvejen 7</t>
+          <t xml:space="preserve">Køjevænget 91</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1361,20 +1361,20 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032620</t>
+          <t xml:space="preserve">10087996</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H23">
-        <v>449</v>
+        <v>1110</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve">311225395</t>
+          <t xml:space="preserve">311225391</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Harevænget 1</t>
+          <t xml:space="preserve">Søndre Tangvej 26</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">8752205</t>
+          <t xml:space="preserve">2092630</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1550,16 +1550,16 @@
         </is>
       </c>
       <c r="H26">
-        <v>658</v>
+        <v>431</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">311225392</t>
+          <t xml:space="preserve">311226040</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-30</t>
+          <t xml:space="preserve">2027-02-01</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndre Tangvej 26</t>
+          <t xml:space="preserve">Kalvebodvej 255</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2092630</t>
+          <t xml:space="preserve">8752208</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1610,16 +1610,16 @@
         </is>
       </c>
       <c r="H27">
-        <v>431</v>
+        <v>1246</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">311226040</t>
+          <t xml:space="preserve">311227426</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-01</t>
+          <t xml:space="preserve">2027-02-09</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kalvebodvej 255</t>
+          <t xml:space="preserve">Engvej 22</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1661,25 +1661,25 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">8752208</t>
+          <t xml:space="preserve">2092475</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H28">
-        <v>1246</v>
+        <v>372</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">311227426</t>
+          <t xml:space="preserve">311228161</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-09</t>
+          <t xml:space="preserve">2027-02-13</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engvej 22</t>
+          <t xml:space="preserve">Rødtjørnen 60C</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1781,25 +1781,25 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2092475</t>
+          <t xml:space="preserve">2092694</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H30">
-        <v>372</v>
+        <v>262</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">311228161</t>
+          <t xml:space="preserve">311245791</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-13</t>
+          <t xml:space="preserve">2027-05-06</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rødtjørnen 60C</t>
+          <t xml:space="preserve">Vestgrønningen 7</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1841,25 +1841,25 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2092694</t>
+          <t xml:space="preserve">2091437</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H31">
-        <v>262</v>
+        <v>382</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">311245791</t>
+          <t xml:space="preserve">311247075</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-06</t>
+          <t xml:space="preserve">2027-05-11</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestgrønningen 7</t>
+          <t xml:space="preserve">Vestgrønningen 11</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1906,20 +1906,20 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H32">
-        <v>382</v>
+        <v>492</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">311247075</t>
+          <t xml:space="preserve">311251338</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-11</t>
+          <t xml:space="preserve">2027-06-01</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestgrønningen 11</t>
+          <t xml:space="preserve">Vestgrønningen 5</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1966,11 +1966,11 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H33">
-        <v>492</v>
+        <v>2044</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestgrønningen 9</t>
+          <t xml:space="preserve">Vestgrønningen 7</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2026,11 +2026,11 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H34">
-        <v>637</v>
+        <v>1136</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestgrønningen 5</t>
+          <t xml:space="preserve">Vestgrønningen 9</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2086,11 +2086,11 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H35">
-        <v>2044</v>
+        <v>637</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestgrønningen 7</t>
+          <t xml:space="preserve">Gl. Havn 2</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2141,25 +2141,25 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2091437</t>
+          <t xml:space="preserve">8752265</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H36">
-        <v>1136</v>
+        <v>263</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">311251338</t>
+          <t xml:space="preserve">311253147</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-01</t>
+          <t xml:space="preserve">2027-06-12</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl. Havn 2</t>
+          <t xml:space="preserve">Strandlinien 3</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2206,15 +2206,15 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H37">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">311253233</t>
+          <t xml:space="preserve">311253129</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandlinien 3</t>
+          <t xml:space="preserve">Kirkevej 8</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2261,25 +2261,25 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">8752265</t>
+          <t xml:space="preserve">2032620</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H38">
-        <v>258</v>
+        <v>560</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">311253233</t>
+          <t xml:space="preserve">311257954</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-12</t>
+          <t xml:space="preserve">2027-06-30</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2326,15 +2326,15 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H39">
-        <v>560</v>
+        <v>549</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">311257954</t>
+          <t xml:space="preserve">311257941</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H40">
-        <v>549</v>
+        <v>339</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2446,11 +2446,11 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H41">
-        <v>339</v>
+        <v>1279</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2506,11 +2506,11 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H42">
-        <v>1279</v>
+        <v>280</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkevej 8</t>
+          <t xml:space="preserve">Ndr Dragørvej 160</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2561,20 +2561,20 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032620</t>
+          <t xml:space="preserve">2033840</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H43">
-        <v>280</v>
+        <v>1074</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">311257941</t>
+          <t xml:space="preserve">311257703</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ndr Dragørvej 160</t>
+          <t xml:space="preserve">Engvej 20A</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033840</t>
+          <t xml:space="preserve">230811, 230812</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2630,16 +2630,16 @@
         </is>
       </c>
       <c r="H44">
-        <v>1074</v>
+        <v>3045</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">311257703</t>
+          <t xml:space="preserve">311293732</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-30</t>
+          <t xml:space="preserve">2028-01-22</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkevej 7</t>
+          <t xml:space="preserve">Kirkevej 11</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2686,15 +2686,15 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H45">
-        <v>3210</v>
+        <v>346</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">311293749</t>
+          <t xml:space="preserve">311293736</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2746,11 +2746,11 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H46">
-        <v>486</v>
+        <v>3210</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkevej 11</t>
+          <t xml:space="preserve">Kirkevej 7</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2806,15 +2806,15 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H47">
-        <v>346</v>
+        <v>486</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">311293736</t>
+          <t xml:space="preserve">311293749</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">

--- a/public/exports/12881517.xlsx
+++ b/public/exports/12881517.xlsx
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">311253129</t>
+          <t xml:space="preserve">311253147</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">311257703</t>
+          <t xml:space="preserve">311257933</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">311293749</t>
+          <t xml:space="preserve">311293736</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">311293749</t>
+          <t xml:space="preserve">311293736</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">

--- a/public/exports/12881517.xlsx
+++ b/public/exports/12881517.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L54"/>
+  <dimension ref="A1:M54"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -59,15 +59,20 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimærkningsfirma</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -124,10 +129,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -184,10 +194,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -244,10 +259,15 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -304,10 +324,15 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -364,10 +389,15 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -424,10 +454,15 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -484,10 +519,15 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -544,10 +584,15 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -604,10 +649,15 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -664,10 +714,15 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -719,15 +774,20 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
+          <t xml:space="preserve">FORCE Technology</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-05-01</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -779,15 +839,20 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-07-04</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -839,15 +904,20 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-09-13</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -899,15 +969,20 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-09-13</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -959,15 +1034,20 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-01-19</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1019,15 +1099,20 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-01-19</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1079,15 +1164,20 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-01-19</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1139,15 +1229,20 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-01-25</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1199,15 +1294,20 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-01-30</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1259,15 +1359,20 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-01-30</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1319,15 +1424,20 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-01-30</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1379,15 +1489,20 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-01-30</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1439,15 +1554,20 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-01-30</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1499,15 +1619,20 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-01-30</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1559,15 +1684,20 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-02-01</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1619,15 +1749,20 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-02-09</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1679,15 +1814,20 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-02-13</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1739,15 +1879,20 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-02-13</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1799,15 +1944,20 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-05-06</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1859,15 +2009,20 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-05-11</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1919,15 +2074,20 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-01</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1979,15 +2139,20 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-01</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2039,15 +2204,20 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-01</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2099,15 +2269,20 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-01</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2154,20 +2329,25 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">311253147</t>
+          <t xml:space="preserve">311253233</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-12</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2214,20 +2394,25 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">311253147</t>
+          <t xml:space="preserve">311253129</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-12</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2279,15 +2464,20 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-30</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2339,15 +2529,20 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-30</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2399,15 +2594,20 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-30</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2459,15 +2659,20 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-30</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2519,15 +2724,20 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-30</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2579,15 +2789,20 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-30</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2639,15 +2854,20 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-01-22</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2699,15 +2919,20 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-01-22</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2759,15 +2984,20 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-01-22</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2819,15 +3049,20 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-01-22</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2879,15 +3114,20 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-03-13</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2939,15 +3179,20 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-03-13</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2999,15 +3244,20 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-03-13</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3059,15 +3309,20 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-08-23</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3119,15 +3374,20 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-08-23</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3179,15 +3439,20 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
+          <t xml:space="preserve">Norca Aps</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-01-13</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3239,21 +3504,26 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
+          <t xml:space="preserve">Norca Aps</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-01-13</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L54" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L54"/>
+  <autoFilter ref="A1:M54"/>
 </worksheet>
 </file>
--- a/public/exports/12881517.xlsx
+++ b/public/exports/12881517.xlsx
@@ -2329,7 +2329,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">311253233</t>
+          <t xml:space="preserve">311253147</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">311257933</t>
+          <t xml:space="preserve">311257703</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
